--- a/reports/member_funnel/downloads/member_funnel_7d_cart_abandon.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_cart_abandon.xlsx
@@ -547,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -575,22 +575,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -631,22 +631,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>lscbo76</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01025029158</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -659,22 +659,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lscbo76</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01025029158</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -687,22 +687,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -715,22 +715,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -911,12 +911,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -939,22 +939,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -967,22 +967,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>zollee77</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01064740702</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -995,22 +995,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1023,22 +1023,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zollee77</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01064740702</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1051,12 +1051,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1079,22 +1079,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1107,22 +1107,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1135,22 +1135,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1163,22 +1163,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1219,22 +1219,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1247,22 +1247,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4822475920</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01073932582</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1275,22 +1275,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1303,12 +1303,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1331,22 +1331,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1359,22 +1359,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1387,22 +1387,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1415,22 +1415,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1443,22 +1443,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4839289649</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01041713878</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1471,12 +1471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_3672780564</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01089459294</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1499,12 +1499,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1527,22 +1527,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_4839289649</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01041713878</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1555,22 +1555,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1583,12 +1583,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4822475920</t>
+          <t>s09635</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01073932582</t>
+          <t>01090472784</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1611,12 +1611,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1667,22 +1667,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4836613952</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01041344927</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1695,22 +1695,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1723,12 +1723,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4326567662</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01046049921</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1751,12 +1751,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1779,12 +1779,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1807,22 +1807,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1835,22 +1835,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4326567662</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01046049921</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1863,22 +1863,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4836613952</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01041344927</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1891,22 +1891,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1919,22 +1919,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4485686054</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01030613096</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1947,22 +1947,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1975,22 +1975,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2003,22 +2003,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4485686054</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01030613096</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2031,22 +2031,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4840292707</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01085257253</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2059,22 +2059,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hw00185</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01032596566</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2087,22 +2087,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>hw00185</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01032596566</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2115,22 +2115,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4840292707</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01085257253</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2171,22 +2171,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2199,22 +2199,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2227,22 +2227,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2255,22 +2255,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2283,22 +2283,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2311,22 +2311,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2367,22 +2367,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4439122782</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01028252500</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2423,22 +2423,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4439122782</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01028252500</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2591,22 +2591,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_3789625265</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01029773942</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2647,22 +2647,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3789625265</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029773942</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2871,12 +2871,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2899,12 +2899,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2927,22 +2927,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>staylus11</t>
+          <t>justicek73</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01055097903</t>
+          <t>01033270931</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2955,22 +2955,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>staylus11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01055097903</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2983,12 +2983,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>justicek73</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01033270931</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3011,22 +3011,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3039,12 +3039,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3067,22 +3067,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3095,22 +3095,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3628696638_2</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01038262132</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3123,22 +3123,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_3628696638_2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01038262132</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3151,12 +3151,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3207,12 +3207,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3235,12 +3235,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3291,12 +3291,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3319,22 +3319,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3347,12 +3347,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3375,12 +3375,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3431,12 +3431,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3487,12 +3487,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3515,22 +3515,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3543,12 +3543,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3571,22 +3571,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3599,22 +3599,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3627,22 +3627,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3655,22 +3655,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3683,22 +3683,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3739,12 +3739,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3767,12 +3767,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3795,22 +3795,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3823,22 +3823,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3879,22 +3879,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3907,22 +3907,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -3935,22 +3935,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3963,22 +3963,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -3991,22 +3991,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4019,22 +4019,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4047,12 +4047,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4075,22 +4075,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4103,12 +4103,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4131,22 +4131,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4159,12 +4159,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4187,22 +4187,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -4215,22 +4215,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4243,22 +4243,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4271,22 +4271,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4299,12 +4299,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -4327,12 +4327,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4355,22 +4355,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4383,12 +4383,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4411,22 +4411,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4439,22 +4439,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4467,22 +4467,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4495,12 +4495,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4523,12 +4523,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4551,12 +4551,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4579,22 +4579,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4607,12 +4607,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -4635,12 +4635,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4663,22 +4663,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4691,22 +4691,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4719,12 +4719,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4747,22 +4747,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4775,12 +4775,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4803,12 +4803,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4831,22 +4831,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4859,12 +4859,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4887,12 +4887,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -4915,12 +4915,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4943,22 +4943,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4999,22 +4999,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5027,12 +5027,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5055,22 +5055,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5083,22 +5083,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5111,12 +5111,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5139,12 +5139,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -5167,12 +5167,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -5195,22 +5195,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5223,22 +5223,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5251,22 +5251,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -5279,22 +5279,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -5307,22 +5307,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5335,12 +5335,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5363,12 +5363,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5391,22 +5391,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5419,22 +5419,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5447,22 +5447,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5503,22 +5503,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5531,22 +5531,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5559,22 +5559,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5587,22 +5587,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5615,22 +5615,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5643,22 +5643,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5671,22 +5671,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5699,22 +5699,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5727,12 +5727,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5755,12 +5755,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5783,22 +5783,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -5811,22 +5811,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -5839,12 +5839,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5867,22 +5867,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -5895,22 +5895,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -5923,22 +5923,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5951,12 +5951,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -5979,22 +5979,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -6007,12 +6007,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6035,22 +6035,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -6119,22 +6119,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_3781116310</t>
+          <t>kk_4659940912</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01052721277</t>
+          <t>01041612810</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6147,22 +6147,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_4659940912</t>
+          <t>kk_3781116310</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01041612810</t>
+          <t>01052721277</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -6231,22 +6231,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4711817746</t>
+          <t>kk_4790306916</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01073740979</t>
+          <t>01093019204</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6259,22 +6259,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4790306916</t>
+          <t>kk_4817994909</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01093019204</t>
+          <t>01085048441</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6287,22 +6287,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4817994909</t>
+          <t>kk_4711817746</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01085048441</t>
+          <t>01073740979</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -6315,12 +6315,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>maria7071</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01090601859</t>
+          <t>01029111071</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6343,12 +6343,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>maria7071</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01029111071</t>
+          <t>01090601859</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6455,22 +6455,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_3186198843</t>
+          <t>kk_4711669963</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01046046000</t>
+          <t>01053480904</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -6483,22 +6483,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_4711669963</t>
+          <t>kk_3186198843</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01053480904</t>
+          <t>01046046000</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6511,12 +6511,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>oh1485</t>
+          <t>nmnlll</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01047621485</t>
+          <t>01026223981</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6539,12 +6539,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_4826700021</t>
+          <t>kk_4684588144</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01066078107</t>
+          <t>01054487450</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6567,12 +6567,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>nmnlll</t>
+          <t>oh1485</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01026223981</t>
+          <t>01047621485</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6595,12 +6595,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_4684588144</t>
+          <t>kk_4826700021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01054487450</t>
+          <t>01066078107</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -6623,22 +6623,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_4824950028</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01077607243</t>
+          <t>01025155876</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -6651,12 +6651,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_4833840470</t>
+          <t>kk_3052471310</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01025155876</t>
+          <t>01095240027</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -6707,22 +6707,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>npko369</t>
+          <t>kk_4824950028</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01037988661</t>
+          <t>01077607243</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -6735,12 +6735,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_3052471310</t>
+          <t>npko369</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01095240027</t>
+          <t>01037988661</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -6791,22 +6791,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_3288126075</t>
+          <t>kk_3466923498</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01049423511</t>
+          <t>01096162200</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -6847,12 +6847,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>heeteak95</t>
+          <t>kk_4815947156</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01099071292</t>
+          <t>01092184392</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -6875,22 +6875,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_4837353288</t>
+          <t>kk_3288126075</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01083028586</t>
+          <t>01049423511</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -6903,12 +6903,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_3466923498</t>
+          <t>king1090</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01096162200</t>
+          <t>01064003306</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -6931,22 +6931,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_3250085369</t>
+          <t>heeteak95</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01096240428</t>
+          <t>01099071292</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -6987,22 +6987,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_4815947156</t>
+          <t>kk_4659340685</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01092184392</t>
+          <t>01063582256</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7015,22 +7015,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>king1090</t>
+          <t>kk_4825970409</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01064003306</t>
+          <t>01071000311</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7043,22 +7043,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_4659340685</t>
+          <t>kk_4837353288</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01063582256</t>
+          <t>01083028586</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7071,22 +7071,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_4825970409</t>
+          <t>kk_3250085369</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01071000311</t>
+          <t>01096240428</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7099,22 +7099,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_3468930697</t>
+          <t>ericm345</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01088808037</t>
+          <t>01055390445</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7127,22 +7127,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_4834068833</t>
+          <t>fubu0084</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01039362991</t>
+          <t>01088780084</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7155,22 +7155,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ericm345</t>
+          <t>kk_2997012029</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01055390445</t>
+          <t>01028601556</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7183,12 +7183,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_3181301935</t>
+          <t>soft908</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01093688332</t>
+          <t>01089622469</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7211,12 +7211,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>soft908</t>
+          <t>kk_3218217013</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01089622469</t>
+          <t>01040864882</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0224</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7295,22 +7295,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_3218217013</t>
+          <t>kk_4834068833</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01040864882</t>
+          <t>01039362991</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -7323,22 +7323,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_2997012029</t>
+          <t>k593083</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01028601556</t>
+          <t>01063997001</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -7351,12 +7351,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>k593083</t>
+          <t>kk_3181301935</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01063997001</t>
+          <t>01093688332</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -7407,12 +7407,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>fubu0084</t>
+          <t>kk_3468930697</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01088780084</t>
+          <t>01088808037</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -7435,22 +7435,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_4313232220</t>
+          <t>storykorea</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01021020310</t>
+          <t>01073710422</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -7463,22 +7463,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>artisthj9504</t>
+          <t>kk_3796558449</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01057969512</t>
+          <t>01027978975</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -7491,17 +7491,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4837508653</t>
+          <t>kk_4838452645</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01076350314</t>
+          <t>01057555796</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7519,22 +7519,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>storykorea</t>
+          <t>limjungwook</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01073710422</t>
+          <t>01087999246</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -7547,22 +7547,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>show5430</t>
+          <t>artisthj9504</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01099500131</t>
+          <t>01057969512</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -7575,22 +7575,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4837521496</t>
+          <t>show5430</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01063580882</t>
+          <t>01099500131</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -7603,17 +7603,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_4837077471</t>
+          <t>kk_4837508653</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01085303077</t>
+          <t>01076350314</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7631,12 +7631,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>jmmj69</t>
+          <t>kk_2752170382</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01056464636</t>
+          <t>01072556480</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_springhiking</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -7659,12 +7659,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>rlrlxodu</t>
+          <t>kk_4605205767</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01032779047</t>
+          <t>01074760700</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -7687,12 +7687,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_2752170382</t>
+          <t>youngv7</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01072556480</t>
+          <t>01030111622</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -7715,12 +7715,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>yiduforce</t>
+          <t>kk_4313232220</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01053350361</t>
+          <t>01021020310</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -7743,12 +7743,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_4838452645</t>
+          <t>kk_4837077471</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01057555796</t>
+          <t>01085303077</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7771,22 +7771,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4605205767</t>
+          <t>maruy22</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01074760700</t>
+          <t>01094898616</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -7799,12 +7799,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>maruy22</t>
+          <t>yiduforce</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01094898616</t>
+          <t>01053350361</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -7827,12 +7827,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>limjungwook</t>
+          <t>jmmj69</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01087999246</t>
+          <t>01056464636</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0401_springhiking</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -7855,22 +7855,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ussu21</t>
+          <t>kk_4837521496</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01027066755</t>
+          <t>01063580882</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -7883,22 +7883,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>youngv7</t>
+          <t>kk_4838209354</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01030111622</t>
+          <t>01082111317</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -7911,22 +7911,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_3796558449</t>
+          <t>rlrlxodu</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01027978975</t>
+          <t>01032779047</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -7939,22 +7939,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4838209354</t>
+          <t>ussu21</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01082111317</t>
+          <t>01027066755</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -7967,12 +7967,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4397620133</t>
+          <t>kk_4837604432</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01034535798</t>
+          <t>01097210211</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -7995,22 +7995,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>woehddl</t>
+          <t>kk_3529523763</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01038760244</t>
+          <t>01085373147</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -8023,22 +8023,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_4838456249</t>
+          <t>kk_3333545995</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01027726748</t>
+          <t>01035495063</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -8051,22 +8051,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_4438159232</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01021662502</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -8079,22 +8079,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_3183680996</t>
+          <t>kk_3828084491</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01027973742</t>
+          <t>01099832284</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -8107,12 +8107,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4837604432</t>
+          <t>ssunya</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01097210211</t>
+          <t>01085089895</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -8135,12 +8135,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kk_4837448431</t>
+          <t>kk_4837197391</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01073131328</t>
+          <t>01033888074</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -8163,22 +8163,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_3348899022</t>
+          <t>swingcool678</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01090504815</t>
+          <t>01035229639</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -8191,22 +8191,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_3150220366</t>
+          <t>kk_4838456249</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01043152346</t>
+          <t>01027726748</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -8219,12 +8219,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ssunya</t>
+          <t>kk_3487203470</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01085089895</t>
+          <t>01046433060</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -8247,12 +8247,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_3333545995</t>
+          <t>kk_3150220366</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01035495063</t>
+          <t>01043152346</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -8275,22 +8275,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_3672393552</t>
+          <t>woehddl</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01054308653</t>
+          <t>01038760244</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -8303,12 +8303,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_3828084491</t>
+          <t>sas159</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01099832284</t>
+          <t>01041922755</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -8331,22 +8331,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sas159</t>
+          <t>kk_4837448431</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01041922755</t>
+          <t>01073131328</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -8359,22 +8359,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_3529523763</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01085373147</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -8387,22 +8387,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>swingcool678</t>
+          <t>kk_4397620133</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01035229639</t>
+          <t>01034535798</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8415,22 +8415,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kk_4438159232</t>
+          <t>kk_3348899022</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01021662502</t>
+          <t>01090504815</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8443,22 +8443,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>kk_3487203470</t>
+          <t>kk_3672393552</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01046433060</t>
+          <t>01054308653</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -8471,22 +8471,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_4837598619</t>
+          <t>kk_3183680996</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01088515202</t>
+          <t>01027973742</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -8499,22 +8499,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>kk_4837197391</t>
+          <t>kk_4837598619</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01033888074</t>
+          <t>01088515202</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -8723,22 +8723,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>kk_3756290261</t>
+          <t>keserase</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01024554001</t>
+          <t>01034114009</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -8751,22 +8751,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>keserase</t>
+          <t>kk_3756290261</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01034114009</t>
+          <t>01024554001</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -8779,22 +8779,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_3735266923</t>
+          <t>soundpia</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01089385514</t>
+          <t>01053382955</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -8807,22 +8807,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>soundpia</t>
+          <t>kk_3735266923</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01053382955</t>
+          <t>01089385514</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -8835,22 +8835,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_4833855255</t>
+          <t>kimsangsup57</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01034118225</t>
+          <t>01053431493</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -8891,22 +8891,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kimsangsup57</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01053431493</t>
+          <t>01034118225</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -8919,12 +8919,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_4835669119</t>
+          <t>baron0787</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01028272862</t>
+          <t>01077616864</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8947,22 +8947,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>baron0787</t>
+          <t>kk_3451376361</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01077616864</t>
+          <t>01089062936</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9031,22 +9031,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>kk_3451376361</t>
+          <t>kk_4835669119</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01089062936</t>
+          <t>01028272862</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
@@ -9087,22 +9087,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4836763027</t>
+          <t>cornflower37</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01086377321</t>
+          <t>01036873378</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -9115,12 +9115,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>codepass</t>
+          <t>kk_4604844467</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01053583130</t>
+          <t>01045678553</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
@@ -9143,22 +9143,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kk_4835743460</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01058882365</t>
+          <t>01084087919</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
@@ -9171,22 +9171,22 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4708231230</t>
+          <t>kk_4836763027</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01097051762</t>
+          <t>01086377321</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
@@ -9199,12 +9199,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>mmy5117</t>
+          <t>kk_3754994737</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01089638283</t>
+          <t>01027236270</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_EFW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
@@ -9227,22 +9227,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_4530113017</t>
+          <t>kk_4835743460</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01064374650</t>
+          <t>01058882365</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
@@ -9255,12 +9255,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>cornflower37</t>
+          <t>kk_4530113017</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01036873378</t>
+          <t>01064374650</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -9283,12 +9283,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>kk_3754994737</t>
+          <t>mmy5117</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01027236270</t>
+          <t>01089638283</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_EFW</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -9311,12 +9311,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_4604844467</t>
+          <t>codepass</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01045678553</t>
+          <t>01053583130</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -9339,22 +9339,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4708231230</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01084087919</t>
+          <t>01097051762</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
@@ -9367,12 +9367,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_4836704387</t>
+          <t>kk_4836975464</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01089735536</t>
+          <t>01033595485</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
@@ -9395,22 +9395,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>kk_4836975464</t>
+          <t>kk_4836899734</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01033595485</t>
+          <t>01081854898</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -9423,12 +9423,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_4836643285</t>
+          <t>ssagagi77</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01025180644</t>
+          <t>01021853260</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9451,22 +9451,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kk_4231959784</t>
+          <t>kk_4836643285</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01035343111</t>
+          <t>01025180644</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -9479,22 +9479,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ssagagi77</t>
+          <t>vtjddn</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01021853260</t>
+          <t>01041346668</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -9507,22 +9507,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>kk_4836450330</t>
+          <t>blueyez</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01022575185</t>
+          <t>01030437573</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -9535,22 +9535,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>kk_4836899734</t>
+          <t>kk_4836838799</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01081854898</t>
+          <t>01064794190</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -9563,12 +9563,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>kk_4836018294</t>
+          <t>gslsjquf</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01052404689</t>
+          <t>01055235265</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
@@ -9591,22 +9591,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_4836838799</t>
+          <t>kk_4836622418</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01064794190</t>
+          <t>01076425021</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E328" t="inlineStr"/>
@@ -9619,22 +9619,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_4460336063</t>
+          <t>ym215215</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01095154870</t>
+          <t>01023353760</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
@@ -9647,12 +9647,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>gslsjquf</t>
+          <t>sangdori76</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01055235265</t>
+          <t>01088651421</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
@@ -9675,22 +9675,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ym215215</t>
+          <t>dsccool</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01023353760</t>
+          <t>01040100422</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
@@ -9703,22 +9703,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>vtjddn</t>
+          <t>kk_4231959784</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01041346668</t>
+          <t>01035343111</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
@@ -9731,12 +9731,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>sangdori76</t>
+          <t>kk_4836704387</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01088651421</t>
+          <t>01089735536</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9759,22 +9759,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>dsccool</t>
+          <t>kk_4460336063</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01040100422</t>
+          <t>01095154870</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
@@ -9787,22 +9787,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_4836622418</t>
+          <t>kk_4836450330</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01076425021</t>
+          <t>01022575185</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
@@ -9815,22 +9815,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>blueyez</t>
+          <t>kk_4836018294</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01030437573</t>
+          <t>01052404689</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
@@ -9899,12 +9899,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_4429073285</t>
+          <t>kk_2921785220</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01024219899</t>
+          <t>01021039178</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -9955,12 +9955,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>kk_2921785220</t>
+          <t>kk_4429073285</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01021039178</t>
+          <t>01024219899</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
@@ -9983,12 +9983,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>kk_4832886393</t>
+          <t>kk_4735583106</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01063709218</t>
+          <t>01053172757</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10011,12 +10011,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>kk_4735583106</t>
+          <t>kk_4832886393</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01053172757</t>
+          <t>01063709218</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10039,22 +10039,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_4833676515</t>
+          <t>kk_2988537551</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01038799958</t>
+          <t>01067477686</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
@@ -10067,12 +10067,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_4234012915</t>
+          <t>ssonggyu</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01091756922</t>
+          <t>01026496431</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E345" t="inlineStr"/>
@@ -10095,12 +10095,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>duqdll</t>
+          <t>kk_4829818548</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>01054658558</t>
+          <t>01083272664</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -10123,22 +10123,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4234012915</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>01083272664</t>
+          <t>01091756922</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -10151,22 +10151,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ssonggyu</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>01026496431</t>
+          <t>01038799958</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
@@ -10179,22 +10179,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>kk_2988537551</t>
+          <t>duqdll</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>01067477686</t>
+          <t>01054658558</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
@@ -10207,22 +10207,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4833968727</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>01045918720</t>
+          <t>01083446112</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E350" t="inlineStr"/>
@@ -10235,12 +10235,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>kk_4791151667</t>
+          <t>kk_3342904159</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>01062417165</t>
+          <t>01087384385</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10263,22 +10263,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>kk_4833968727</t>
+          <t>wsshoon</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>01083446112</t>
+          <t>01052387200</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -10291,12 +10291,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>wsshoon</t>
+          <t>kk_4829567584</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>01052387200</t>
+          <t>01050892873</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
@@ -10319,12 +10319,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>kk_4824069339</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>01050892873</t>
+          <t>01085619182</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
@@ -10347,12 +10347,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>kk_3342904159</t>
+          <t>kk_4791151667</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>01087384385</t>
+          <t>01062417165</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10375,12 +10375,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>kk_4824069339</t>
+          <t>kk_4828953106</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>01085619182</t>
+          <t>01045918720</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -10403,12 +10403,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>kk_4833693850</t>
+          <t>jihgih</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>01038159698</t>
+          <t>01089757461</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -10431,12 +10431,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>kk_4806347273</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>01058059653</t>
+          <t>01047460729</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -10459,22 +10459,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>eegyul</t>
+          <t>kk_4806347273</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>01082074139</t>
+          <t>01058059653</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -10487,12 +10487,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>kk_4834235896</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>01047460729</t>
+          <t>01052127971</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10515,12 +10515,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>kk_4834235896</t>
+          <t>kk_4833693850</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>01052127971</t>
+          <t>01038159698</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -10543,12 +10543,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>leeks1224</t>
+          <t>rejina74</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>01097011224</t>
+          <t>01029302995</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -10571,22 +10571,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>kk_4833586139</t>
+          <t>eegyul</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>01094980753</t>
+          <t>01082074139</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -10599,12 +10599,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>kk_2934597824</t>
+          <t>kk_4833428925</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>01048132345</t>
+          <t>01033851974</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -10627,22 +10627,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>jihgih</t>
+          <t>kk_4833586139</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>01089757461</t>
+          <t>01094980753</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -10655,22 +10655,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>kk_4833428925</t>
+          <t>leeks1224</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>01033851974</t>
+          <t>01097011224</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -10683,22 +10683,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>rejina74</t>
+          <t>kk_2934597824</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>01029302995</t>
+          <t>01048132345</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -10711,12 +10711,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>man345</t>
+          <t>kwangh22</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>01025254013</t>
+          <t>01062680616</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -10739,12 +10739,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>andy52</t>
+          <t>kk_4508896829</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>01074048800</t>
+          <t>01063629833</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -10767,22 +10767,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>kk_4835156745</t>
+          <t>kk_4835462666</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>01098182311</t>
+          <t>01025263630</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -10795,22 +10795,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>kk_4508896829</t>
+          <t>kk_4834271394</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>01063629833</t>
+          <t>01089067428</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -10823,12 +10823,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>kwangh22</t>
+          <t>andy52</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>01062680616</t>
+          <t>01074048800</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -10851,12 +10851,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>kk_4835462666</t>
+          <t>man345</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>01025263630</t>
+          <t>01025254013</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -10879,22 +10879,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>kk_4834271394</t>
+          <t>kk_4833995564</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>01089067428</t>
+          <t>01056380026</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -10907,12 +10907,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>kk_4833995564</t>
+          <t>kk_4835156745</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>01056380026</t>
+          <t>01098182311</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11103,12 +11103,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>kk_3765059726</t>
+          <t>kk_3814176758</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>01029636547</t>
+          <t>01098841586</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11131,12 +11131,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>kk_3814176758</t>
+          <t>kk_3765059726</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>01098841586</t>
+          <t>01029636547</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11187,22 +11187,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>kk_4733250727</t>
+          <t>kjh7508</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>01082204399</t>
+          <t>01055000782</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -11243,22 +11243,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>kjh7508</t>
+          <t>kk_4733250727</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>01055000782</t>
+          <t>01082204399</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -11271,12 +11271,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>kk_4797424044</t>
+          <t>ing106</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>01022539818</t>
+          <t>01099047122</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11299,22 +11299,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ing106</t>
+          <t>kk_3186100939</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>01099047122</t>
+          <t>01050160957</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -11327,12 +11327,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>kk_3186100939</t>
+          <t>hyunlee30</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>01050160957</t>
+          <t>01050225476</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -11355,17 +11355,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>hyunlee30</t>
+          <t>kk_4797424044</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>01050225476</t>
+          <t>01022539818</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -11383,22 +11383,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>kk_3751847516</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>01084439111</t>
+          <t>01073999165</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -11411,22 +11411,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4805758485</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>01048512958</t>
+          <t>01072213694</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -11439,22 +11439,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_3751847516</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>01073999165</t>
+          <t>01084439111</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
@@ -11467,22 +11467,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>kk_4805758485</t>
+          <t>eastehdwk</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>01072213694</t>
+          <t>01084434416</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
@@ -11495,12 +11495,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>eastehdwk</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>01084434416</t>
+          <t>01048512958</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
@@ -11523,12 +11523,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>kk_3238130489</t>
+          <t>kk_4533872627</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>01091372550</t>
+          <t>01073370126</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
@@ -11579,12 +11579,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>kk_4533872627</t>
+          <t>kk_3796868235</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>01073370126</t>
+          <t>01032084557</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
@@ -11607,12 +11607,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>kk_3796868235</t>
+          <t>kk_3238130489</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01032084557</t>
+          <t>01091372550</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11635,22 +11635,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>rzh82</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01091881895</t>
+          <t>01055027830</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -11663,22 +11663,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>rzh82</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>01055027830</t>
+          <t>01091881895</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -11691,22 +11691,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>also5</t>
+          <t>gamani1</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>01034023481</t>
+          <t>01058654215</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0406</t>
         </is>
       </c>
       <c r="E403" t="inlineStr"/>
@@ -11719,22 +11719,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>01050909606</t>
+          <t>01083876673</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E404" t="inlineStr"/>
@@ -11747,22 +11747,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>kch0315</t>
+          <t>kk_4617802380</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>01095358188</t>
+          <t>01057311238</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E405" t="inlineStr"/>
@@ -11775,22 +11775,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>kk_4617802380</t>
+          <t>ayo8881</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>01057311238</t>
+          <t>01037541059</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0406</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -11803,12 +11803,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>shin2002318</t>
+          <t>also5</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>01091422318</t>
+          <t>01034023481</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E407" t="inlineStr"/>
@@ -11831,22 +11831,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>kk_4832804456</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>01083876673</t>
+          <t>01050909606</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E408" t="inlineStr"/>
@@ -11859,22 +11859,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01066685269</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E409" t="inlineStr"/>
@@ -11887,22 +11887,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ayo8881</t>
+          <t>shin2002318</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>01037541059</t>
+          <t>01091422318</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>EDM_0406</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E410" t="inlineStr"/>
@@ -11915,22 +11915,22 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>gamani1</t>
+          <t>kch0315</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>01058654215</t>
+          <t>01095358188</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>EDM_0406</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -11971,22 +11971,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>01066685269</t>
+          <t>01064620979</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -11999,22 +11999,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ohwalnim</t>
+          <t>kk_3140286618</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>01062017224</t>
+          <t>01063026643</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -12027,22 +12027,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>01064620979</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -12055,22 +12055,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>kk_3140286618</t>
+          <t>ohwalnim</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>01063026643</t>
+          <t>01062017224</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
@@ -12139,22 +12139,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>chan680</t>
+          <t>lsc3022</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>01026244284</t>
+          <t>01064159003</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
@@ -12195,22 +12195,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>lsc3022</t>
+          <t>chan680</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>01064159003</t>
+          <t>01026244284</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
@@ -12251,22 +12251,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>kk_4799691410</t>
+          <t>dreambyland</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>01089330548</t>
+          <t>01066439111</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
@@ -12279,22 +12279,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>dreambyland</t>
+          <t>kk_4799691410</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>01066439111</t>
+          <t>01089330548</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
@@ -12307,22 +12307,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>kk_4753453482</t>
+          <t>kk_4827915654</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>01091699883</t>
+          <t>01033317065</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E425" t="inlineStr"/>
@@ -12335,12 +12335,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>zozonim</t>
+          <t>kk_4818417743</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>01086001090</t>
+          <t>01040582392</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E426" t="inlineStr"/>
@@ -12363,22 +12363,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>kk_4827915654</t>
+          <t>zozonim</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>01033317065</t>
+          <t>01086001090</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -12391,12 +12391,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>kk_4818417743</t>
+          <t>kk_4753453482</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>01040582392</t>
+          <t>01091699883</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
@@ -12419,22 +12419,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>kk_3639045388</t>
+          <t>bkh1117</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>01064334743</t>
+          <t>01028397712</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
@@ -12447,22 +12447,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>bkh1117</t>
+          <t>kk_3639045388</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>01028397712</t>
+          <t>01064334743</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
@@ -12503,12 +12503,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>kk_3859761959</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>01066452742</t>
+          <t>01087818173</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12531,12 +12531,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_3859761959</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>01087818173</t>
+          <t>01066452742</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12615,12 +12615,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>nicetrip</t>
+          <t>ssj1213</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>01053184996</t>
+          <t>01085659044</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -12643,22 +12643,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_3587602578</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>01065549054</t>
+          <t>01065888698</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -12671,22 +12671,22 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>kk_3587602578</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>01065888698</t>
+          <t>01062744365</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -12699,22 +12699,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_2875930422</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>01062744365</t>
+          <t>01088264888</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -12727,22 +12727,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>kk_2875930422</t>
+          <t>kk_4829077261</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>01088264888</t>
+          <t>01065549054</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -12755,12 +12755,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>ssj1213</t>
+          <t>kk_4710916911</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>01085659044</t>
+          <t>01045439878</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -12783,12 +12783,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>kk_4710916911</t>
+          <t>nicetrip</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>01045439878</t>
+          <t>01053184996</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -12811,22 +12811,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>mijung2327</t>
+          <t>kk_3240065465</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>01099160314</t>
+          <t>01094896664</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -12839,12 +12839,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>sty31933</t>
+          <t>kk_2966069807</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>01059637276</t>
+          <t>01093630362</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -12867,22 +12867,22 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>kk_3240065465</t>
+          <t>mijung2327</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>01094896664</t>
+          <t>01099160314</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E445" t="inlineStr"/>
@@ -12895,12 +12895,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>kk_2966069807</t>
+          <t>kk_4705947160</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>01093630362</t>
+          <t>01049101018</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
@@ -12923,12 +12923,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>kk_4705947160</t>
+          <t>sty31933</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>01049101018</t>
+          <t>01059637276</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -12951,22 +12951,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>01035267762</t>
+          <t>01040295064</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -12979,22 +12979,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_3648118311</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>01023232572</t>
+          <t>01044883174</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
@@ -13007,22 +13007,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>takgirl</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>01086676090</t>
+          <t>01086266995</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13035,22 +13035,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>01046719677</t>
+          <t>01090481510</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
@@ -13063,22 +13063,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_3182584661</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>01040295064</t>
+          <t>01029893640</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
@@ -13091,12 +13091,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>takgirl</t>
+          <t>hjm0714</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>01086266995</t>
+          <t>01035150714</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13119,22 +13119,22 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>injeon</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>01090481510</t>
+          <t>01064280419</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -13147,12 +13147,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>kk_3648118311</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>01044883174</t>
+          <t>01046719677</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -13175,22 +13175,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>kk_3182584661</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>01029893640</t>
+          <t>01086676090</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
@@ -13203,22 +13203,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>01046428717</t>
+          <t>01035267762</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13231,22 +13231,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>hjm0714</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>01035150714</t>
+          <t>01046428717</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13259,22 +13259,22 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>injeon</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>01064280419</t>
+          <t>01023232572</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
